--- a/data/trans_dic/P1413-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1413-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,03</t>
+          <t>2,42; 6,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,63</t>
+          <t>1,21; 4,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 10,79</t>
+          <t>2,12; 9,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,89</t>
+          <t>3,12; 6,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,33</t>
+          <t>2,27; 6,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,61</t>
+          <t>1,44; 4,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 16,53</t>
+          <t>5,38; 15,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,79</t>
+          <t>3,15; 5,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,54</t>
+          <t>2,11; 4,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,68</t>
+          <t>0,85; 2,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 10,52</t>
+          <t>4,69; 10,53</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 9,29</t>
+          <t>5,35; 9,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,76</t>
+          <t>3,27; 6,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,74</t>
+          <t>1,61; 4,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,62; 10,98</t>
+          <t>4,46; 10,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 12,28</t>
+          <t>7,46; 12,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,07; 10,62</t>
+          <t>5,97; 10,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,93; 7,85</t>
+          <t>3,93; 7,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 13,88</t>
+          <t>8,19; 14,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 10,07</t>
+          <t>6,84; 10,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 7,84</t>
+          <t>4,96; 7,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 5,57</t>
+          <t>3,1; 5,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,28; 11,09</t>
+          <t>7,25; 11,46</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,81; 17,13</t>
+          <t>11,7; 17,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 8,19</t>
+          <t>4,54; 8,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 9,14</t>
+          <t>4,97; 9,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,94; 13,46</t>
+          <t>7,79; 12,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,56; 16,91</t>
+          <t>11,56; 16,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,67; 16,06</t>
+          <t>10,56; 15,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,7; 11,03</t>
+          <t>6,7; 11,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,09; 23,77</t>
+          <t>18,14; 23,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,47; 16,14</t>
+          <t>12,36; 16,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,18; 11,36</t>
+          <t>7,97; 11,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,39; 9,44</t>
+          <t>6,45; 9,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,83; 17,8</t>
+          <t>13,69; 17,79</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>24,57%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,27; 23,03</t>
+          <t>16,14; 23,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 12,2</t>
+          <t>6,79; 11,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 11,85</t>
+          <t>7,07; 11,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 21,73</t>
+          <t>17,31; 23,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,66; 26,9</t>
+          <t>19,27; 26,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,46; 21,14</t>
+          <t>14,37; 20,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,94; 16,21</t>
+          <t>10,83; 16,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,14; 30,33</t>
+          <t>26,08; 31,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,56; 23,49</t>
+          <t>18,72; 23,77</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,36; 15,65</t>
+          <t>11,37; 15,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,58; 13,11</t>
+          <t>9,43; 13,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,61; 24,94</t>
+          <t>22,54; 26,59</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,84%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,72; 34,6</t>
+          <t>26,01; 35,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,23; 16,1</t>
+          <t>9,45; 15,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,71; 16,1</t>
+          <t>9,56; 16,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,31; 31,24</t>
+          <t>22,95; 29,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,99; 31,0</t>
+          <t>21,58; 30,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,78; 30,83</t>
+          <t>21,77; 30,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,37; 24,78</t>
+          <t>17,5; 25,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,05; 42,4</t>
+          <t>36,35; 42,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,38; 31,59</t>
+          <t>25,47; 31,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,94; 22,34</t>
+          <t>16,88; 22,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,56; 19,72</t>
+          <t>14,4; 19,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,58; 35,42</t>
+          <t>30,55; 35,31</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>37,23%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21,35; 31,72</t>
+          <t>21,7; 31,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,28; 23,85</t>
+          <t>14,76; 23,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,66; 16,97</t>
+          <t>10,03; 17,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,08; 30,52</t>
+          <t>23,24; 30,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32,35; 42,25</t>
+          <t>32,74; 42,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,86; 36,21</t>
+          <t>26,42; 36,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,43; 26,2</t>
+          <t>17,41; 25,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44,38; 83,41</t>
+          <t>43,48; 50,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28,62; 35,82</t>
+          <t>28,89; 35,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22,31; 29,11</t>
+          <t>22,43; 29,15</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,84; 20,78</t>
+          <t>14,96; 20,42</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35,91; 73,03</t>
+          <t>34,9; 39,92</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,59%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,69; 41,13</t>
+          <t>28,99; 41,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,82; 28,23</t>
+          <t>16,52; 27,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,37; 24,36</t>
+          <t>15,14; 24,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35,18; 43,82</t>
+          <t>34,96; 44,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,69; 41,44</t>
+          <t>31,05; 41,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,02; 44,6</t>
+          <t>34,01; 44,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,7; 35,76</t>
+          <t>25,43; 35,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>53,53; 60,46</t>
+          <t>54,41; 61,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31,09; 39,31</t>
+          <t>31,15; 39,45</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28,5; 36,39</t>
+          <t>28,77; 36,2</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22,29; 30,02</t>
+          <t>22,84; 30,23</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,29; 52,74</t>
+          <t>47,82; 53,34</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,99; 17,44</t>
+          <t>14,99; 17,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,14; 10,08</t>
+          <t>7,95; 10,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,25; 9,16</t>
+          <t>7,25; 9,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,49; 19,36</t>
+          <t>17,22; 20,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,82; 20,49</t>
+          <t>17,81; 20,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,94; 19,53</t>
+          <t>16,87; 19,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,78; 15,29</t>
+          <t>12,75; 15,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>29,25; 45,44</t>
+          <t>29,32; 31,92</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,88; 18,67</t>
+          <t>16,78; 18,63</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12,84; 14,52</t>
+          <t>12,83; 14,6</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,33; 11,87</t>
+          <t>10,4; 11,95</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,91; 34,86</t>
+          <t>23,85; 25,64</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18393</t>
+          <t>20495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31375</t>
+          <t>34715</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49768</t>
+          <t>55210</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12487; 29806</t>
+          <t>11947; 29870</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5818; 21016</t>
+          <t>5507; 19836</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 7724</t>
+          <t>0; 7713</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5610; 43169</t>
+          <t>8627; 39951</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14993; 32200</t>
+          <t>14609; 32179</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9854; 27230</t>
+          <t>9771; 25844</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5629; 18229</t>
+          <t>5706; 18581</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18933; 51760</t>
+          <t>19501; 54532</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30947; 55722</t>
+          <t>30319; 56108</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18367; 40123</t>
+          <t>18632; 40452</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7686; 21826</t>
+          <t>6968; 20315</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32060; 75007</t>
+          <t>36135; 81102</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29879</t>
+          <t>33415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>51528</t>
+          <t>55399</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81407</t>
+          <t>88814</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39110; 68343</t>
+          <t>39363; 67498</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22019; 46468</t>
+          <t>22450; 45872</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9435; 27962</t>
+          <t>9485; 27462</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19479; 46272</t>
+          <t>21184; 50809</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46602; 76825</t>
+          <t>46668; 77773</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37073; 64797</t>
+          <t>36420; 65802</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22130; 44233</t>
+          <t>22159; 44909</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32239; 70984</t>
+          <t>41060; 71629</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>94093; 137028</t>
+          <t>93135; 136330</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64158; 101687</t>
+          <t>64322; 101417</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36234; 64279</t>
+          <t>35752; 63466</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>58556; 103404</t>
+          <t>70732; 111776</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57066</t>
+          <t>64289</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>112637</t>
+          <t>129436</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>169703</t>
+          <t>193725</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>75441; 109393</t>
+          <t>74726; 110203</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30861; 55814</t>
+          <t>30986; 56823</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34340; 61125</t>
+          <t>33274; 60294</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42524; 72116</t>
+          <t>48308; 80093</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>79713; 116643</t>
+          <t>79719; 116527</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75682; 113938</t>
+          <t>74912; 112241</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44306; 72945</t>
+          <t>44296; 73962</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>98031; 128773</t>
+          <t>112742; 149089</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>165646; 214435</t>
+          <t>164135; 214332</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>113845; 158112</t>
+          <t>110923; 157749</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>84981; 125592</t>
+          <t>85753; 125651</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>148960; 191783</t>
+          <t>169919; 220797</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>132391</t>
+          <t>142109</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>193156</t>
+          <t>210594</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>325546</t>
+          <t>352703</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>84440; 119560</t>
+          <t>83786; 119651</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42655; 74981</t>
+          <t>41715; 71041</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46545; 76556</t>
+          <t>45668; 75247</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55384; 192661</t>
+          <t>121038; 163179</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>101364; 138697</t>
+          <t>99364; 136494</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>88827; 129838</t>
+          <t>88245; 126836</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71011; 105199</t>
+          <t>70313; 104578</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>164727; 215871</t>
+          <t>191897; 229205</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>192011; 243058</t>
+          <t>193722; 245938</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>139543; 192361</t>
+          <t>139677; 188811</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124050; 169840</t>
+          <t>122093; 170173</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>185568; 398713</t>
+          <t>323434; 381614</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>153242</t>
+          <t>160917</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>213669</t>
+          <t>238127</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>366911</t>
+          <t>399044</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>99470; 133783</t>
+          <t>100570; 135600</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>39651; 69158</t>
+          <t>40592; 67145</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46421; 76942</t>
+          <t>45692; 77258</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136186; 174998</t>
+          <t>139599; 181506</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>88855; 125236</t>
+          <t>87193; 124974</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>97546; 138048</t>
+          <t>97505; 135678</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86303; 123113</t>
+          <t>86968; 124671</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>196351; 230938</t>
+          <t>220551; 257346</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>200704; 249754</t>
+          <t>201366; 251421</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>148604; 195977</t>
+          <t>148049; 195707</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>141894; 192205</t>
+          <t>140342; 189428</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>337951; 391364</t>
+          <t>371255; 429042</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>99323</t>
+          <t>109620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>388406</t>
+          <t>205118</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>487729</t>
+          <t>314738</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>62477; 92807</t>
+          <t>63494; 92516</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>44242; 73884</t>
+          <t>45711; 74212</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32311; 56743</t>
+          <t>33528; 58613</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>84823; 112146</t>
+          <t>94422; 124757</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>110933; 144883</t>
+          <t>112278; 144162</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>95099; 128176</t>
+          <t>93530; 127728</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>65841; 98978</t>
+          <t>65761; 97175</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>269997; 507415</t>
+          <t>190967; 221240</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>181903; 227615</t>
+          <t>183577; 227891</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>148106; 193199</t>
+          <t>148860; 193521</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>105700; 147990</t>
+          <t>106494; 145401</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>350391; 712604</t>
+          <t>295061; 337484</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>111767</t>
+          <t>123432</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>242893</t>
+          <t>268546</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>354660</t>
+          <t>391977</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>60218; 86327</t>
+          <t>60851; 86510</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>42015; 70535</t>
+          <t>41287; 69546</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>39496; 62595</t>
+          <t>38903; 62900</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>99476; 123916</t>
+          <t>108456; 137418</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>102486; 138369</t>
+          <t>103694; 139517</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>132346; 173496</t>
+          <t>132286; 172162</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>102844; 143087</t>
+          <t>101782; 141805</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>227957; 257456</t>
+          <t>252814; 283471</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>169062; 213774</t>
+          <t>169393; 214535</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>182036; 232446</t>
+          <t>183806; 231262</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>146480; 197249</t>
+          <t>150087; 198648</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>335094; 373697</t>
+          <t>370478; 413309</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>602060</t>
+          <t>654276</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1233663</t>
+          <t>1141936</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1835724</t>
+          <t>1796212</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>491205; 571470</t>
+          <t>491274; 578124</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>278887; 345582</t>
+          <t>272492; 346774</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>246051; 310896</t>
+          <t>245974; 309842</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>465913; 668553</t>
+          <t>607107; 705157</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>602194; 692257</t>
+          <t>601826; 696772</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>602211; 694407</t>
+          <t>599804; 695235</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>453078; 541806</t>
+          <t>451864; 539195</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1069708; 1662016</t>
+          <t>1093870; 1190892</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1123590; 1242838</t>
+          <t>1116665; 1239970</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>896548; 1013551</t>
+          <t>895592; 1019284</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>716938; 823410</t>
+          <t>721383; 829037</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1629138; 2479075</t>
+          <t>1731327; 1860958</t>
         </is>
       </c>
     </row>
